--- a/dash-3dof.xlsx
+++ b/dash-3dof.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,7 +35,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -58,9 +64,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,6 +435,10 @@
   </sheetPr>
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -442,24 +453,24 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Pagetitle</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>msl3dof ENG-01 telemetry</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>PageTop</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t># msl3dof ENG-01
 Nominal engagement: 5202 m initial range, 271.774 m/s missile, slow crossing target. Closest approach 4.117 m at t = 19.191 s.
@@ -468,36 +479,36 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>PageBottom</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Generated from `out/ENG-01/`. Rebuild the run with `./build/linux-release/msl3dof_sim scenarios/ENG-01.json`.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Datafile</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Density</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>compact</t>
         </is>
@@ -514,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B75"/>
+  <dimension ref="A1:B85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -522,150 +533,150 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Required to be present in the file</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Not read and ignored, NaN in the data sheet</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Optional, use default values if cell is clear</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Height</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Height of the plot in the browser</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Datafile</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>File path to the data file for this graph. If the it has the keyword 'master', the file specified on the header sheet is used.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>xLabel</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Graph x-axis label</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>xValue</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>CSV column name used for x values</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Any number of graphs allowed, specified by sets:</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>xSliderStep</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Resolution for the x-axis slider</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Graph title</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>yLabel</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Graph y-axis label</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>CSV column name(s) used for y values, any number allowed</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Mode</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>lines or markers+lines</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Default is lines</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>If the rectangle tool is required in the graph, markers must be added.
 For large data sets this will slow down the rendering!</t>
@@ -673,12 +684,12 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>MarkerOpacity</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Marker opacity
 Handy to set to 0, then markers do not show but the rectangle tool is available</t>
@@ -686,429 +697,512 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>For large data sets use the default set to {'opacity': 0}</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Format</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Hover text formatting, default if not given .4f</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>This is valid for each graph, value provided on graph xLabel &amp; yLabel lines</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Dash</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>solid' 'dash', 'longdash', 'dot', 'dashdot', 'longdashdot' or leave empty for solid line</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Default if not given: use solid line</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Linewidth</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Linewidth is the line width in pt</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Default if not given: use plotly default value of 2</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Scale</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Default if not given: 1</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Offset</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Default if not given: 0</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Colour</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>colour can have many different formats: CSS or RGB style</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>rgb(67,67,67)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>rgba(0,100,80,0.2)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>https://community.plot.ly/t/plotly-colours-list/11730/3</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>https://www.w3schools.com/cssref/css_colors.asp</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>https://www.rapidtables.com/web/css/css-color.html</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Default if not given: plotly will assign its own colours</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>LineLabel</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Legend for the line. </t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>Default if not given: name of signal</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>GraphType</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>line'  or 'bar', I am not sure what other options are available and useful</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Default if not given: use 'line'</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>GraphTop</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>If present insert this Markdown just in front of the graph</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>GraphBottom</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>If present insert this Markdown just after the graph</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Include</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>True or False: Include this graph, default True</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>ToDisk</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>True or False: Save as html, default True</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>UseSubplots</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>True or False: Handle grpahs sets as sub-plots of one graphs, default False</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>Notes:</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>If the rendering fails, check that there are no cells with values below the intended valid range. As a precaution 'clear contents' for all cells below the intended valid range.</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>Added in the browser-only version:</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>commonX</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>True or False: tie every graph on this tab to one x scale, default False</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>Zoom, pan or autoscale any graph and all the others follow.</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>Click or rubber-band select on any graph and every box on the tab fills at that x.</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>Each box quotes its own nearest recorded sample; nothing is interpolated.</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>Only graphs on the same tab are linked, and only if the tab is Included.</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Categories</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>Ordered state names for a text column, drawn as an enumeration</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>Comma separated here, a JSON list in a .json config: Cueing, Tracking</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>Default if not given: order of first appearance in the data</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>A value in the data but missing from the list is appended, never dropped</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>Datafile (on a yValue row)</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>Data file for this line only, overriding the sheet Datafile</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>This is how one tab carries signals recorded at different rates</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>Density (header sheet)</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>'compact' or 'comfortable', default 'compact'</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>compact removes the space between graphs and draws the title inside the plot</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>Multi-rate JSON data</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>A .json data file may hold named groups, one per sample rate</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>Select one by appending a fragment: data/run.json#gimbal_1ms</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>A plain list of samples still means one single-rate table, as before</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Text columns</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>Plotted as enumerations: labels on the y axis, drawn as steps</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>Scale and Offset are ignored for an enumeration</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Changed 2026-09-11:</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Also opens a BLOCK: rows below it apply to the graphs below it</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>A second Height starts a new block, which may name its own Datafile</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>A block inherits xValue and xLabel from above if it does not set them</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>This is how one tab carries several data files at different rates</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>UseSubplots</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>REMOVED. Had been disabled for some time. Use blocks and commonX instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>xSliderStep</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>REMOVED with the x-axis slider.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>X range boxes</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Beside each graph: type a start and an end, Apply to zoom, Reset to undo</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Replaces the old slider. On a commonX tab it drives every graph on the tab.</t>
         </is>
       </c>
     </row>
@@ -1203,73 +1297,73 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Height</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="2" t="n">
         <v>260</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Datafile</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>../systemCHandbook/CB_3dof/out/ENG-01/body.json</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>xLabel</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Time [s]</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>.4f</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>xValue</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>t</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>commonX</t>
         </is>
       </c>
-      <c r="B6" t="b">
+      <c r="B6" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>GraphTop</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>### body
 Point-mass translational dynamics, 10 ms.</t>
@@ -1277,247 +1371,247 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Position, world NED</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>yLabel</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Position [m]</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>.6f</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>px</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>North</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>py</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>East</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>pz</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>yLabel</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>V [m/s]</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>.6f</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Flight path angles</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>yLabel</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Angle [rad]</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>.6f</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>gamma</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>gamma, climb</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>chi</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>chi, heading</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Body mode</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>yLabel</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>mode</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>.6f</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>mode</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Include</t>
         </is>
       </c>
-      <c r="B23" t="b">
+      <c r="B23" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>ToDisk</t>
         </is>
       </c>
-      <c r="B24" t="b">
+      <c r="B24" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1612,73 +1706,73 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Height</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="2" t="n">
         <v>260</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Datafile</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>../systemCHandbook/CB_3dof/out/ENG-01/target.json</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>xLabel</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Time [s]</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>.4f</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>xValue</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>t</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>commonX</t>
         </is>
       </c>
-      <c r="B6" t="b">
+      <c r="B6" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>GraphTop</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>### target
 Predefined target trajectory, 10 ms.</t>
@@ -1686,182 +1780,182 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Position, world NED</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>yLabel</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Position [m]</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>.6f</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>px</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>North</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>py</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>East</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>pz</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Velocity, world NED</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>yLabel</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Velocity [m/s]</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>.6f</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>vx</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>North</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>vy</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>East</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>vz</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Include</t>
         </is>
       </c>
-      <c r="B18" t="b">
+      <c r="B18" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>ToDisk</t>
         </is>
       </c>
-      <c r="B19" t="b">
+      <c r="B19" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1956,73 +2050,73 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Height</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="2" t="n">
         <v>260</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Datafile</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>../systemCHandbook/CB_3dof/out/ENG-01/gimbal.json</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>xLabel</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Time [s]</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>.4f</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>xValue</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>t</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>commonX</t>
         </is>
       </c>
-      <c r="B6" t="b">
+      <c r="B6" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>GraphTop</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>### gimbal
 Seeker gimbal, 1 ms. The fastest signal in the run.</t>
@@ -2030,206 +2124,206 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Gimbal angles</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>yLabel</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Angle [rad]</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>.6f</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>phi_g</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>roll</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>theta_g</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>pitch</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>psi_g</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>yaw</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Travel margin</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>yLabel</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Margin [rad]</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>.6f</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>gim_margin_pitch</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>pitch</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>gim_margin_yaw</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>yaw</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Allocation feasible</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>yLabel</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>feasible</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>.6f</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>gim_feasible</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Include</t>
         </is>
       </c>
-      <c r="B20" t="b">
+      <c r="B20" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>ToDisk</t>
         </is>
       </c>
-      <c r="B21" t="b">
+      <c r="B21" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2324,73 +2418,73 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Height</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="2" t="n">
         <v>260</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Datafile</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>../systemCHandbook/CB_3dof/out/ENG-01/camera.json</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>xLabel</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Time [s]</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>.4f</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>xValue</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>t</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>commonX</t>
         </is>
       </c>
-      <c r="B6" t="b">
+      <c r="B6" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>GraphTop</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>### camera
 Seeker sensor, 20 ms. The slowest signal in the run.</t>
@@ -2398,85 +2492,85 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Tracking error, sensor frame</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>yLabel</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Error [rad]</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>.6f</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>eps_y</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>eps_y, elevation about y_S</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>eps_z</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>eps_z, azimuth about z_S</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Include</t>
         </is>
       </c>
-      <c r="B12" t="b">
+      <c r="B12" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>ToDisk</t>
         </is>
       </c>
-      <c r="B13" t="b">
+      <c r="B13" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2571,73 +2665,73 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Height</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="2" t="n">
         <v>260</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Datafile</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>../systemCHandbook/CB_3dof/out/ENG-01/tracker.json</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>xLabel</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Time [s]</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>.4f</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>xValue</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>t</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>commonX</t>
         </is>
       </c>
-      <c r="B6" t="b">
+      <c r="B6" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>GraphTop</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>### tracker
 Track loop, 10 ms.</t>
@@ -2645,126 +2739,126 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Measured tracking error</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>yLabel</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Error [rad]</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>.6f</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>eps_my</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>eps_my</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>eps_mz</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>eps_mz</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Commanded roll rate</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>yLabel</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Rate [rad/s]</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>.6f</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>omega_roll_c</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Include</t>
         </is>
       </c>
-      <c r="B15" t="b">
+      <c r="B15" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>ToDisk</t>
         </is>
       </c>
-      <c r="B16" t="b">
+      <c r="B16" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2859,73 +2953,73 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Height</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="2" t="n">
         <v>260</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Datafile</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>../systemCHandbook/CB_3dof/out/ENG-01/guidance_computer.json</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>xLabel</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Time [s]</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>.4f</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>xValue</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>t</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>commonX</t>
         </is>
       </c>
-      <c r="B6" t="b">
+      <c r="B6" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>GraphTop</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>### guidance_computer
 Guidance filter and proportional navigation, 10 ms.</t>
@@ -2933,182 +3027,182 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Commanded lateral acceleration</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>yLabel</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Acceleration [m/s^2]</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>.6f</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>a_cx</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>a_cy</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>y</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>a_cz</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Filtered LOS rate</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>yLabel</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Rate [rad/s]</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>.6f</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>los_rate_x</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>los_rate_y</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>y</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>los_rate_z</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Include</t>
         </is>
       </c>
-      <c r="B18" t="b">
+      <c r="B18" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>ToDisk</t>
         </is>
       </c>
-      <c r="B19" t="b">
+      <c r="B19" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3203,73 +3297,73 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Height</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="2" t="n">
         <v>260</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Datafile</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>../systemCHandbook/CB_3dof/out/ENG-01/flight_control.json</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>xLabel</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Time [s]</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>.4f</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>xValue</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>t</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>commonX</t>
         </is>
       </c>
-      <c r="B6" t="b">
+      <c r="B6" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>GraphTop</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>### flight_control
 Achieved specific force after the lag, 10 ms.</t>
@@ -3277,102 +3371,102 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Achieved specific force, world</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>yLabel</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Specific force [m/s^2]</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>.6f</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>f_ach_x</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>f_ach_y</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>y</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>f_ach_z</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Include</t>
         </is>
       </c>
-      <c r="B13" t="b">
+      <c r="B13" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>ToDisk</t>
         </is>
       </c>
-      <c r="B14" t="b">
+      <c r="B14" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3467,73 +3561,73 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Height</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="2" t="n">
         <v>260</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Datafile</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>../systemCHandbook/CB_3dof/out/ENG-01/missile_controller.json</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>xLabel</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Time [s]</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>.4f</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>xValue</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>t</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>commonX</t>
         </is>
       </c>
-      <c r="B6" t="b">
+      <c r="B6" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>GraphTop</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>### missile_controller
 Cueing/Tracking mode control, 2 ms.</t>
@@ -3541,145 +3635,145 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Engagement mode</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>yLabel</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>mode</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>.6f</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>mode</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Roll pointing error</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>yLabel</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Error [rad]</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>.6f</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>roll_pointing_error</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Flight control command active</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>yLabel</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>.6f</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>yValue</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>flight_control_cmd_active</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Include</t>
         </is>
       </c>
-      <c r="B17" t="b">
+      <c r="B17" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>ToDisk</t>
         </is>
       </c>
-      <c r="B18" t="b">
+      <c r="B18" s="2" t="b">
         <v>0</v>
       </c>
     </row>
